--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M549"/>
+  <dimension ref="A1:M550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25149,6 +25149,51 @@
         <v>378.26</v>
       </c>
       <c r="M549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>396.85</v>
+      </c>
+      <c r="C550" t="n">
+        <v>395.05</v>
+      </c>
+      <c r="D550" t="n">
+        <v>391.74</v>
+      </c>
+      <c r="E550" t="n">
+        <v>392.36</v>
+      </c>
+      <c r="F550" t="n">
+        <v>391.52</v>
+      </c>
+      <c r="G550" t="n">
+        <v>393.17</v>
+      </c>
+      <c r="H550" t="n">
+        <v>396.13</v>
+      </c>
+      <c r="I550" t="n">
+        <v>392.52</v>
+      </c>
+      <c r="J550" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="K550" t="n">
+        <v>378.52</v>
+      </c>
+      <c r="L550" t="n">
+        <v>376.52</v>
+      </c>
+      <c r="M550" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25165,7 +25210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30878,6 +30923,16 @@
       </c>
       <c r="B571" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -31046,28 +31101,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.10822549822868</v>
+        <v>-0.1087537102870055</v>
       </c>
       <c r="J2" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K2" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01100337962576248</v>
+        <v>0.01115400165260338</v>
       </c>
       <c r="M2" t="n">
-        <v>6.375312535095525</v>
+        <v>6.366568576656613</v>
       </c>
       <c r="N2" t="n">
-        <v>59.35117301422129</v>
+        <v>59.24692537738141</v>
       </c>
       <c r="O2" t="n">
-        <v>7.703971249571307</v>
+        <v>7.697202438378596</v>
       </c>
       <c r="P2" t="n">
-        <v>401.1487142734277</v>
+        <v>401.1539855171202</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31124,28 +31179,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0791694653185287</v>
+        <v>-0.08061470159053963</v>
       </c>
       <c r="J3" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K3" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006991076644720651</v>
+        <v>0.007272000555821445</v>
       </c>
       <c r="M3" t="n">
-        <v>5.539246784644857</v>
+        <v>5.536533663326902</v>
       </c>
       <c r="N3" t="n">
-        <v>50.19100823429781</v>
+        <v>50.12848343818079</v>
       </c>
       <c r="O3" t="n">
-        <v>7.084561259125212</v>
+        <v>7.080147133935903</v>
       </c>
       <c r="P3" t="n">
-        <v>401.1194966570954</v>
+        <v>401.1339192596523</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31202,28 +31257,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03962903832960674</v>
+        <v>-0.04149668362277884</v>
       </c>
       <c r="J4" t="n">
+        <v>549</v>
+      </c>
+      <c r="K4" t="n">
         <v>548</v>
       </c>
-      <c r="K4" t="n">
-        <v>547</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.002663773364847799</v>
+        <v>0.002927639065914089</v>
       </c>
       <c r="M4" t="n">
-        <v>4.695351295874289</v>
+        <v>4.695460689725718</v>
       </c>
       <c r="N4" t="n">
-        <v>33.15764226117879</v>
+        <v>33.14543999119505</v>
       </c>
       <c r="O4" t="n">
-        <v>5.758267296781106</v>
+        <v>5.757207655729907</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9390832916618</v>
+        <v>397.9577320427388</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31280,28 +31335,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02803844991458513</v>
+        <v>-0.02892045589821141</v>
       </c>
       <c r="J5" t="n">
+        <v>549</v>
+      </c>
+      <c r="K5" t="n">
         <v>548</v>
       </c>
-      <c r="K5" t="n">
-        <v>547</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.001374663203737359</v>
+        <v>0.001467848980225561</v>
       </c>
       <c r="M5" t="n">
-        <v>4.606800086626311</v>
+        <v>4.602585885037884</v>
       </c>
       <c r="N5" t="n">
-        <v>32.20523894068463</v>
+        <v>32.15724335789827</v>
       </c>
       <c r="O5" t="n">
-        <v>5.674965985861468</v>
+        <v>5.67073569811698</v>
       </c>
       <c r="P5" t="n">
-        <v>395.5292288992438</v>
+        <v>395.5380358767235</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31358,28 +31413,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1213168888093912</v>
+        <v>-0.1215704944082819</v>
       </c>
       <c r="J6" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K6" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03179458940754154</v>
+        <v>0.03204851392725017</v>
       </c>
       <c r="M6" t="n">
-        <v>4.186573976574234</v>
+        <v>4.180169928031334</v>
       </c>
       <c r="N6" t="n">
-        <v>25.26726418283914</v>
+        <v>25.22212984768172</v>
       </c>
       <c r="O6" t="n">
-        <v>5.02665536742267</v>
+        <v>5.022163861094311</v>
       </c>
       <c r="P6" t="n">
-        <v>395.407305625781</v>
+        <v>395.4098364595484</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31436,28 +31491,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0457533312141441</v>
+        <v>-0.04540987964008591</v>
       </c>
       <c r="J7" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K7" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004493316126996327</v>
+        <v>0.004444128555484594</v>
       </c>
       <c r="M7" t="n">
-        <v>3.951742471791159</v>
+        <v>3.946395568757282</v>
       </c>
       <c r="N7" t="n">
-        <v>26.14713165285667</v>
+        <v>26.10113681182108</v>
       </c>
       <c r="O7" t="n">
-        <v>5.113426605795439</v>
+        <v>5.108927168380959</v>
       </c>
       <c r="P7" t="n">
-        <v>393.4228906406805</v>
+        <v>393.419463197261</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31514,28 +31569,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06463828744136783</v>
+        <v>0.06688700591323768</v>
       </c>
       <c r="J8" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K8" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007664125798980348</v>
+        <v>0.008216705297234062</v>
       </c>
       <c r="M8" t="n">
-        <v>4.262226269315542</v>
+        <v>4.264775201052232</v>
       </c>
       <c r="N8" t="n">
-        <v>30.49840720291002</v>
+        <v>30.51281576172462</v>
       </c>
       <c r="O8" t="n">
-        <v>5.522536301638045</v>
+        <v>5.523840671283399</v>
       </c>
       <c r="P8" t="n">
-        <v>388.2137692597653</v>
+        <v>388.1913283804362</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31592,28 +31647,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05750776729825336</v>
+        <v>0.05944814878310264</v>
       </c>
       <c r="J9" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K9" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005452465299772169</v>
+        <v>0.005839179519090409</v>
       </c>
       <c r="M9" t="n">
-        <v>4.749546861021593</v>
+        <v>4.751366211988044</v>
       </c>
       <c r="N9" t="n">
-        <v>34.00846707504785</v>
+        <v>33.99861171384365</v>
       </c>
       <c r="O9" t="n">
-        <v>5.831677895344345</v>
+        <v>5.830832849074277</v>
       </c>
       <c r="P9" t="n">
-        <v>385.651018115438</v>
+        <v>385.6316542567342</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31670,28 +31725,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09276507736944173</v>
+        <v>-0.09168894612328297</v>
       </c>
       <c r="J10" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K10" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01265821815768486</v>
+        <v>0.01241453865571951</v>
       </c>
       <c r="M10" t="n">
-        <v>4.970983754478732</v>
+        <v>4.967224357079487</v>
       </c>
       <c r="N10" t="n">
-        <v>37.84124094947064</v>
+        <v>37.78833540398845</v>
       </c>
       <c r="O10" t="n">
-        <v>6.151523465733561</v>
+        <v>6.147221763039662</v>
       </c>
       <c r="P10" t="n">
-        <v>384.3347337218206</v>
+        <v>384.3239945689478</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31748,28 +31803,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08204607930382828</v>
+        <v>-0.08179124758082121</v>
       </c>
       <c r="J11" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K11" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01015363461798136</v>
+        <v>0.01013184645294751</v>
       </c>
       <c r="M11" t="n">
-        <v>4.693139365860961</v>
+        <v>4.685705537569936</v>
       </c>
       <c r="N11" t="n">
-        <v>36.99672955434954</v>
+        <v>36.93023869779415</v>
       </c>
       <c r="O11" t="n">
-        <v>6.082493695380993</v>
+        <v>6.077025481088108</v>
       </c>
       <c r="P11" t="n">
-        <v>379.9702369452383</v>
+        <v>379.967693875478</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31826,28 +31881,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08572176795200846</v>
+        <v>-0.08588960145013962</v>
       </c>
       <c r="J12" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K12" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007667855298890247</v>
+        <v>0.00772881790635549</v>
       </c>
       <c r="M12" t="n">
-        <v>5.716632229528087</v>
+        <v>5.706999468461202</v>
       </c>
       <c r="N12" t="n">
-        <v>53.61259124443396</v>
+        <v>53.51532596387685</v>
       </c>
       <c r="O12" t="n">
-        <v>7.322061953058985</v>
+        <v>7.315417005467074</v>
       </c>
       <c r="P12" t="n">
-        <v>379.231164739412</v>
+        <v>379.2328396183823</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31885,7 +31940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M549"/>
+  <dimension ref="A1:M550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68663,6 +68718,73 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-42.05965332118064,171.36379929187146</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-42.05899123525871,171.36390746612418</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-42.05833062350597,171.36403377675163</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-42.057666149897145,171.36411288327196</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-42.057003101431285,171.36420952584663</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-42.056337603659316,171.36427626140133</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-42.05567081404196,171.3643272634229</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>-42.05501046172728,171.3644571752886</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>-42.05435405516295,171.36463548817326</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>-42.05369638602237,171.36479842603453</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-42.053034433489906,171.36490899805585</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M550"/>
+  <dimension ref="A1:M551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25194,6 +25194,51 @@
         <v>376.52</v>
       </c>
       <c r="M550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>400.57</v>
+      </c>
+      <c r="C551" t="n">
+        <v>399.19</v>
+      </c>
+      <c r="D551" t="n">
+        <v>393.25</v>
+      </c>
+      <c r="E551" t="n">
+        <v>395.12</v>
+      </c>
+      <c r="F551" t="n">
+        <v>394.88</v>
+      </c>
+      <c r="G551" t="n">
+        <v>396.99</v>
+      </c>
+      <c r="H551" t="n">
+        <v>396.47</v>
+      </c>
+      <c r="I551" t="n">
+        <v>391.23</v>
+      </c>
+      <c r="J551" t="n">
+        <v>383.44</v>
+      </c>
+      <c r="K551" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="L551" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="M551" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25210,7 +25255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B572"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30933,6 +30978,16 @@
       </c>
       <c r="B572" t="n">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -31101,28 +31156,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1087537102870055</v>
+        <v>-0.1079187388131461</v>
       </c>
       <c r="J2" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K2" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01115400165260338</v>
+        <v>0.01102877414051517</v>
       </c>
       <c r="M2" t="n">
-        <v>6.366568576656613</v>
+        <v>6.358800184364476</v>
       </c>
       <c r="N2" t="n">
-        <v>59.24692537738141</v>
+        <v>59.14868138997237</v>
       </c>
       <c r="O2" t="n">
-        <v>7.697202438378596</v>
+        <v>7.690817992253644</v>
       </c>
       <c r="P2" t="n">
-        <v>401.1539855171202</v>
+        <v>401.1455953385496</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31179,28 +31234,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08061470159053963</v>
+        <v>-0.08054737658302351</v>
       </c>
       <c r="J3" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K3" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007272000555821445</v>
+        <v>0.007289964080399169</v>
       </c>
       <c r="M3" t="n">
-        <v>5.536533663326902</v>
+        <v>5.526795974579381</v>
       </c>
       <c r="N3" t="n">
-        <v>50.12848343818079</v>
+        <v>50.03740235968437</v>
       </c>
       <c r="O3" t="n">
-        <v>7.080147133935903</v>
+        <v>7.073712063668154</v>
       </c>
       <c r="P3" t="n">
-        <v>401.1339192596523</v>
+        <v>401.1332427469175</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31257,28 +31312,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04149668362277884</v>
+        <v>-0.04281348319830511</v>
       </c>
       <c r="J4" t="n">
+        <v>550</v>
+      </c>
+      <c r="K4" t="n">
         <v>549</v>
       </c>
-      <c r="K4" t="n">
-        <v>548</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.002927639065914089</v>
+        <v>0.003126511488225181</v>
       </c>
       <c r="M4" t="n">
-        <v>4.695460689725718</v>
+        <v>4.692971431135235</v>
       </c>
       <c r="N4" t="n">
-        <v>33.14543999119505</v>
+        <v>33.10865941653861</v>
       </c>
       <c r="O4" t="n">
-        <v>5.757207655729907</v>
+        <v>5.754012462320412</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9577320427388</v>
+        <v>397.9709716643302</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31335,28 +31390,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02892045589821141</v>
+        <v>-0.02879616866736575</v>
       </c>
       <c r="J5" t="n">
+        <v>550</v>
+      </c>
+      <c r="K5" t="n">
         <v>549</v>
       </c>
-      <c r="K5" t="n">
-        <v>548</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.001467848980225561</v>
+        <v>0.00146131854106657</v>
       </c>
       <c r="M5" t="n">
-        <v>4.602585885037884</v>
+        <v>4.594854392026339</v>
       </c>
       <c r="N5" t="n">
-        <v>32.15724335789827</v>
+        <v>32.09887933240729</v>
       </c>
       <c r="O5" t="n">
-        <v>5.67073569811698</v>
+        <v>5.665587289276133</v>
       </c>
       <c r="P5" t="n">
-        <v>395.5380358767235</v>
+        <v>395.5367862439505</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31413,28 +31468,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1215704944082819</v>
+        <v>-0.1205934326791843</v>
       </c>
       <c r="J6" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K6" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03204851392725017</v>
+        <v>0.03166310500298153</v>
       </c>
       <c r="M6" t="n">
-        <v>4.180169928031334</v>
+        <v>4.177621791512191</v>
       </c>
       <c r="N6" t="n">
-        <v>25.22212984768172</v>
+        <v>25.18924930102693</v>
       </c>
       <c r="O6" t="n">
-        <v>5.022163861094311</v>
+        <v>5.018889249727167</v>
       </c>
       <c r="P6" t="n">
-        <v>395.4098364595484</v>
+        <v>395.4000184925421</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31491,28 +31546,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04540987964008591</v>
+        <v>-0.04367026317006911</v>
       </c>
       <c r="J7" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K7" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004444128555484594</v>
+        <v>0.004122098194557555</v>
       </c>
       <c r="M7" t="n">
-        <v>3.946395568757282</v>
+        <v>3.948461241405462</v>
       </c>
       <c r="N7" t="n">
-        <v>26.10113681182108</v>
+        <v>26.0948204069214</v>
       </c>
       <c r="O7" t="n">
-        <v>5.108927168380959</v>
+        <v>5.108308957661174</v>
       </c>
       <c r="P7" t="n">
-        <v>393.419463197261</v>
+        <v>393.401982728425</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31569,28 +31624,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06688700591323768</v>
+        <v>0.06926335768246078</v>
       </c>
       <c r="J8" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K8" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008216705297234062</v>
+        <v>0.008820015082345645</v>
       </c>
       <c r="M8" t="n">
-        <v>4.264775201052232</v>
+        <v>4.267751138215115</v>
       </c>
       <c r="N8" t="n">
-        <v>30.51281576172462</v>
+        <v>30.53410603658384</v>
       </c>
       <c r="O8" t="n">
-        <v>5.523840671283399</v>
+        <v>5.525767461320087</v>
       </c>
       <c r="P8" t="n">
-        <v>388.1913283804362</v>
+        <v>388.1674497015659</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31647,28 +31702,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05944814878310264</v>
+        <v>0.0609156701803738</v>
       </c>
       <c r="J9" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K9" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005839179519090409</v>
+        <v>0.006149343773594662</v>
       </c>
       <c r="M9" t="n">
-        <v>4.751366211988044</v>
+        <v>4.750533565895556</v>
       </c>
       <c r="N9" t="n">
-        <v>33.99861171384365</v>
+        <v>33.96607317536139</v>
       </c>
       <c r="O9" t="n">
-        <v>5.830832849074277</v>
+        <v>5.828041967536043</v>
       </c>
       <c r="P9" t="n">
-        <v>385.6316542567342</v>
+        <v>385.616907924716</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31725,28 +31780,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09168894612328297</v>
+        <v>-0.09112857925224134</v>
       </c>
       <c r="J10" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K10" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01241453865571951</v>
+        <v>0.01231420487443391</v>
       </c>
       <c r="M10" t="n">
-        <v>4.967224357079487</v>
+        <v>4.960909052639043</v>
       </c>
       <c r="N10" t="n">
-        <v>37.78833540398845</v>
+        <v>37.72389812538424</v>
       </c>
       <c r="O10" t="n">
-        <v>6.147221763039662</v>
+        <v>6.141978355984677</v>
       </c>
       <c r="P10" t="n">
-        <v>384.3239945689478</v>
+        <v>384.318363744111</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31803,28 +31858,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08179124758082121</v>
+        <v>-0.08153491475810959</v>
       </c>
       <c r="J11" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K11" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01013184645294751</v>
+        <v>0.01011036093706774</v>
       </c>
       <c r="M11" t="n">
-        <v>4.685705537569936</v>
+        <v>4.678289397246907</v>
       </c>
       <c r="N11" t="n">
-        <v>36.93023869779415</v>
+        <v>36.86398604870394</v>
       </c>
       <c r="O11" t="n">
-        <v>6.077025481088108</v>
+        <v>6.071571958620267</v>
       </c>
       <c r="P11" t="n">
-        <v>379.967693875478</v>
+        <v>379.9651181250202</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31881,28 +31936,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08588960145013962</v>
+        <v>-0.08598027992247469</v>
       </c>
       <c r="J12" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K12" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00772881790635549</v>
+        <v>0.007777019420259768</v>
       </c>
       <c r="M12" t="n">
-        <v>5.706999468461202</v>
+        <v>5.697037756415748</v>
       </c>
       <c r="N12" t="n">
-        <v>53.51532596387685</v>
+        <v>53.41813715217805</v>
       </c>
       <c r="O12" t="n">
-        <v>7.315417005467074</v>
+        <v>7.308771247766484</v>
       </c>
       <c r="P12" t="n">
-        <v>379.2328396183823</v>
+        <v>379.2337507975055</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31940,7 +31995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M550"/>
+  <dimension ref="A1:M551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68785,6 +68840,73 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-42.059649672188485,171.3637546095247</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-42.05898717432419,171.36385773950576</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-42.058329142364414,171.36401563993223</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-42.05766344266232,171.36407973287203</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-42.05699980569569,171.3641691692529</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-42.056333856742725,171.3642303802732</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-42.055670480548905,171.3643231798045</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-42.05501172702193,171.36447266886</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>-42.05435546755973,171.36465278314918</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>-42.05369639583053,171.3647985461373</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-42.053034237328696,171.36490659602472</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M551"/>
+  <dimension ref="A1:M552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25239,6 +25239,51 @@
         <v>376.72</v>
       </c>
       <c r="M551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:37+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>401.78</v>
+      </c>
+      <c r="C552" t="n">
+        <v>399.2</v>
+      </c>
+      <c r="D552" t="n">
+        <v>397.22</v>
+      </c>
+      <c r="E552" t="n">
+        <v>399.74</v>
+      </c>
+      <c r="F552" t="n">
+        <v>399.1</v>
+      </c>
+      <c r="G552" t="n">
+        <v>398.2</v>
+      </c>
+      <c r="H552" t="n">
+        <v>396.13</v>
+      </c>
+      <c r="I552" t="n">
+        <v>388.23</v>
+      </c>
+      <c r="J552" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="K552" t="n">
+        <v>376.08</v>
+      </c>
+      <c r="L552" t="n">
+        <v>377.09</v>
+      </c>
+      <c r="M552" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25255,7 +25300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30988,6 +31033,16 @@
       </c>
       <c r="B573" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -31156,28 +31211,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1079187388131461</v>
+        <v>-0.1066457693654849</v>
       </c>
       <c r="J2" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K2" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01102877414051517</v>
+        <v>0.01081346628128754</v>
       </c>
       <c r="M2" t="n">
-        <v>6.358800184364476</v>
+        <v>6.353017662816327</v>
       </c>
       <c r="N2" t="n">
-        <v>59.14868138997237</v>
+        <v>59.06334251945083</v>
       </c>
       <c r="O2" t="n">
-        <v>7.690817992253644</v>
+        <v>7.685267888593788</v>
       </c>
       <c r="P2" t="n">
-        <v>401.1455953385496</v>
+        <v>401.1327689555528</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31234,28 +31289,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08054737658302351</v>
+        <v>-0.08047613162788327</v>
       </c>
       <c r="J3" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K3" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007289964080399169</v>
+        <v>0.007307352145545676</v>
       </c>
       <c r="M3" t="n">
-        <v>5.526795974579381</v>
+        <v>5.517110646691242</v>
       </c>
       <c r="N3" t="n">
-        <v>50.03740235968437</v>
+        <v>49.94665931741454</v>
       </c>
       <c r="O3" t="n">
-        <v>7.073712063668154</v>
+        <v>7.067295049551458</v>
       </c>
       <c r="P3" t="n">
-        <v>401.1332427469175</v>
+        <v>401.1325248859485</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31312,28 +31367,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04281348319830511</v>
+        <v>-0.04267390399996907</v>
       </c>
       <c r="J4" t="n">
+        <v>551</v>
+      </c>
+      <c r="K4" t="n">
         <v>550</v>
       </c>
-      <c r="K4" t="n">
-        <v>549</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.003126511488225181</v>
+        <v>0.003119131378337969</v>
       </c>
       <c r="M4" t="n">
-        <v>4.692971431135235</v>
+        <v>4.685181725035455</v>
       </c>
       <c r="N4" t="n">
-        <v>33.10865941653861</v>
+        <v>33.04872670128568</v>
       </c>
       <c r="O4" t="n">
-        <v>5.754012462320412</v>
+        <v>5.748802197091641</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9709716643302</v>
+        <v>397.9695644329947</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31390,28 +31445,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02879616866736575</v>
+        <v>-0.02698662252576445</v>
       </c>
       <c r="J5" t="n">
+        <v>551</v>
+      </c>
+      <c r="K5" t="n">
         <v>550</v>
       </c>
-      <c r="K5" t="n">
-        <v>549</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.00146131854106657</v>
+        <v>0.001287228331547818</v>
       </c>
       <c r="M5" t="n">
-        <v>4.594854392026339</v>
+        <v>4.595963919221258</v>
       </c>
       <c r="N5" t="n">
-        <v>32.09887933240729</v>
+        <v>32.08503141480038</v>
       </c>
       <c r="O5" t="n">
-        <v>5.665587289276133</v>
+        <v>5.664365049570903</v>
       </c>
       <c r="P5" t="n">
-        <v>395.5367862439505</v>
+        <v>395.518542479378</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31468,28 +31523,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1205934326791843</v>
+        <v>-0.1180805906558419</v>
       </c>
       <c r="J6" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K6" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03166310500298153</v>
+        <v>0.03041958142890289</v>
       </c>
       <c r="M6" t="n">
-        <v>4.177621791512191</v>
+        <v>4.182937955136311</v>
       </c>
       <c r="N6" t="n">
-        <v>25.18924930102693</v>
+        <v>25.22929578338232</v>
       </c>
       <c r="O6" t="n">
-        <v>5.018889249727167</v>
+        <v>5.022877241520274</v>
       </c>
       <c r="P6" t="n">
-        <v>395.4000184925421</v>
+        <v>395.3746992091444</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31546,28 +31601,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04367026317006911</v>
+        <v>-0.04150216511430624</v>
       </c>
       <c r="J7" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K7" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004122098194557555</v>
+        <v>0.003730844047824089</v>
       </c>
       <c r="M7" t="n">
-        <v>3.948461241405462</v>
+        <v>3.952732767231817</v>
       </c>
       <c r="N7" t="n">
-        <v>26.0948204069214</v>
+        <v>26.11130571996195</v>
       </c>
       <c r="O7" t="n">
-        <v>5.108308957661174</v>
+        <v>5.10992228120565</v>
       </c>
       <c r="P7" t="n">
-        <v>393.401982728425</v>
+        <v>393.3801370697653</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31624,28 +31679,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06926335768246078</v>
+        <v>0.07149871762480824</v>
       </c>
       <c r="J8" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K8" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008820015082345645</v>
+        <v>0.009411202926716267</v>
       </c>
       <c r="M8" t="n">
-        <v>4.267751138215115</v>
+        <v>4.270025476793968</v>
       </c>
       <c r="N8" t="n">
-        <v>30.53410603658384</v>
+        <v>30.54655736045263</v>
       </c>
       <c r="O8" t="n">
-        <v>5.525767461320087</v>
+        <v>5.526894006623669</v>
       </c>
       <c r="P8" t="n">
-        <v>388.1674497015659</v>
+        <v>388.1449263151571</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31702,28 +31757,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0609156701803738</v>
+        <v>0.06128229570978177</v>
       </c>
       <c r="J9" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K9" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006149343773594662</v>
+        <v>0.006248639431949421</v>
       </c>
       <c r="M9" t="n">
-        <v>4.750533565895556</v>
+        <v>4.743848794512458</v>
       </c>
       <c r="N9" t="n">
-        <v>33.96607317536139</v>
+        <v>33.90625437750381</v>
       </c>
       <c r="O9" t="n">
-        <v>5.828041967536043</v>
+        <v>5.822907725312485</v>
       </c>
       <c r="P9" t="n">
-        <v>385.616907924716</v>
+        <v>385.6132138223437</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31780,28 +31835,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09112857925224134</v>
+        <v>-0.09111551221728124</v>
       </c>
       <c r="J10" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K10" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01231420487443391</v>
+        <v>0.01236153631109904</v>
       </c>
       <c r="M10" t="n">
-        <v>4.960909052639043</v>
+        <v>4.951968776709221</v>
       </c>
       <c r="N10" t="n">
-        <v>37.72389812538424</v>
+        <v>37.65543601956973</v>
       </c>
       <c r="O10" t="n">
-        <v>6.141978355984677</v>
+        <v>6.136402530764237</v>
       </c>
       <c r="P10" t="n">
-        <v>384.318363744111</v>
+        <v>384.3182320812534</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31858,28 +31913,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08153491475810959</v>
+        <v>-0.0821643003955177</v>
       </c>
       <c r="J11" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K11" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01011036093706774</v>
+        <v>0.01030641657274045</v>
       </c>
       <c r="M11" t="n">
-        <v>4.678289397246907</v>
+        <v>4.673341175433577</v>
       </c>
       <c r="N11" t="n">
-        <v>36.86398604870394</v>
+        <v>36.8024624597394</v>
       </c>
       <c r="O11" t="n">
-        <v>6.071571958620267</v>
+        <v>6.066503314079652</v>
       </c>
       <c r="P11" t="n">
-        <v>379.9651181250202</v>
+        <v>379.9714597864426</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31936,28 +31991,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08598027992247469</v>
+        <v>-0.08593175188788159</v>
       </c>
       <c r="J12" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K12" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007777019420259768</v>
+        <v>0.007800523111338054</v>
       </c>
       <c r="M12" t="n">
-        <v>5.697037756415748</v>
+        <v>5.6869585128699</v>
       </c>
       <c r="N12" t="n">
-        <v>53.41813715217805</v>
+        <v>53.32122152010486</v>
       </c>
       <c r="O12" t="n">
-        <v>7.308771247766484</v>
+        <v>7.30213814715285</v>
       </c>
       <c r="P12" t="n">
-        <v>379.2337507975055</v>
+        <v>379.2332618312079</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31995,7 +32050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M551"/>
+  <dimension ref="A1:M552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68907,6 +68962,73 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:37+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-42.059648485281386,171.36374007575185</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-42.05898716451514,171.3638576193932</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-42.05832524822366,171.36396795571616</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-42.057658910965294,171.3640242419922</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-42.056995666388715,171.36411848329948</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-42.05633266988837,171.36421584724695</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-42.05567081404196,171.3643272634229</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-42.05501466955959,171.364508700424</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>-42.05435693880361,171.36467079874996</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>-42.053698779210215,171.36482773111544</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-42.053033874430334,171.36490215226718</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M552"/>
+  <dimension ref="A1:M553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25284,6 +25284,51 @@
         <v>377.09</v>
       </c>
       <c r="M552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>402.79</v>
+      </c>
+      <c r="C553" t="n">
+        <v>401.12</v>
+      </c>
+      <c r="D553" t="n">
+        <v>398.94</v>
+      </c>
+      <c r="E553" t="n">
+        <v>401.86</v>
+      </c>
+      <c r="F553" t="n">
+        <v>402.6</v>
+      </c>
+      <c r="G553" t="n">
+        <v>401.49</v>
+      </c>
+      <c r="H553" t="n">
+        <v>398.73</v>
+      </c>
+      <c r="I553" t="n">
+        <v>389.07</v>
+      </c>
+      <c r="J553" t="n">
+        <v>382.69</v>
+      </c>
+      <c r="K553" t="n">
+        <v>378.86</v>
+      </c>
+      <c r="L553" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="M553" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25300,7 +25345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B574"/>
+  <dimension ref="A1:B575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31043,6 +31088,16 @@
       </c>
       <c r="B574" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -31211,28 +31266,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1066457693654849</v>
+        <v>-0.1050098403195117</v>
       </c>
       <c r="J2" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K2" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01081346628128754</v>
+        <v>0.01052485653347668</v>
       </c>
       <c r="M2" t="n">
-        <v>6.353017662816327</v>
+        <v>6.348866372167878</v>
       </c>
       <c r="N2" t="n">
-        <v>59.06334251945083</v>
+        <v>58.99262756846855</v>
       </c>
       <c r="O2" t="n">
-        <v>7.685267888593788</v>
+        <v>7.680665828459701</v>
       </c>
       <c r="P2" t="n">
-        <v>401.1327689555528</v>
+        <v>401.1162367884553</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31289,28 +31344,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08047613162788327</v>
+        <v>-0.07970379785906162</v>
       </c>
       <c r="J3" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K3" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007307352145545676</v>
+        <v>0.007197481120157057</v>
       </c>
       <c r="M3" t="n">
-        <v>5.517110646691242</v>
+        <v>5.51082631666524</v>
       </c>
       <c r="N3" t="n">
-        <v>49.94665931741454</v>
+        <v>49.86426337181788</v>
       </c>
       <c r="O3" t="n">
-        <v>7.067295049551458</v>
+        <v>7.061463259963751</v>
       </c>
       <c r="P3" t="n">
-        <v>401.1325248859485</v>
+        <v>401.1247199319667</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31367,28 +31422,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04267390399996907</v>
+        <v>-0.04190787895859643</v>
       </c>
       <c r="J4" t="n">
+        <v>552</v>
+      </c>
+      <c r="K4" t="n">
         <v>551</v>
       </c>
-      <c r="K4" t="n">
-        <v>550</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.003119131378337969</v>
+        <v>0.003020343545969362</v>
       </c>
       <c r="M4" t="n">
-        <v>4.685181725035455</v>
+        <v>4.680729395749706</v>
       </c>
       <c r="N4" t="n">
-        <v>33.04872670128568</v>
+        <v>32.99670973321244</v>
       </c>
       <c r="O4" t="n">
-        <v>5.748802197091641</v>
+        <v>5.744276258434342</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9695644329947</v>
+        <v>397.9618185798057</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31445,28 +31500,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02698662252576445</v>
+        <v>-0.02441238315547667</v>
       </c>
       <c r="J5" t="n">
+        <v>552</v>
+      </c>
+      <c r="K5" t="n">
         <v>551</v>
       </c>
-      <c r="K5" t="n">
-        <v>550</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.001287228331547818</v>
+        <v>0.001055066912332703</v>
       </c>
       <c r="M5" t="n">
-        <v>4.595963919221258</v>
+        <v>4.601054943458334</v>
       </c>
       <c r="N5" t="n">
-        <v>32.08503141480038</v>
+        <v>32.11672273296537</v>
       </c>
       <c r="O5" t="n">
-        <v>5.664365049570903</v>
+        <v>5.667161788140989</v>
       </c>
       <c r="P5" t="n">
-        <v>395.518542479378</v>
+        <v>395.4925124161834</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31523,28 +31578,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1180805906558419</v>
+        <v>-0.1143064174385608</v>
       </c>
       <c r="J6" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K6" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03041958142890289</v>
+        <v>0.02846513987145771</v>
       </c>
       <c r="M6" t="n">
-        <v>4.182937955136311</v>
+        <v>4.194902911757469</v>
       </c>
       <c r="N6" t="n">
-        <v>25.22929578338232</v>
+        <v>25.37671095320923</v>
       </c>
       <c r="O6" t="n">
-        <v>5.022877241520274</v>
+        <v>5.037530243403928</v>
       </c>
       <c r="P6" t="n">
-        <v>395.3746992091444</v>
+        <v>395.3365586415955</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31601,28 +31656,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04150216511430624</v>
+        <v>-0.03814587716299542</v>
       </c>
       <c r="J7" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K7" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003730844047824089</v>
+        <v>0.00314844638124101</v>
       </c>
       <c r="M7" t="n">
-        <v>3.952732767231817</v>
+        <v>3.963147660108437</v>
       </c>
       <c r="N7" t="n">
-        <v>26.11130571996195</v>
+        <v>26.21672510671257</v>
       </c>
       <c r="O7" t="n">
-        <v>5.10992228120565</v>
+        <v>5.12022705616778</v>
       </c>
       <c r="P7" t="n">
-        <v>393.3801370697653</v>
+        <v>393.3462195148597</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31679,28 +31734,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07149871762480824</v>
+        <v>0.07466682527530835</v>
       </c>
       <c r="J8" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K8" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009411202926716267</v>
+        <v>0.01025227541190554</v>
       </c>
       <c r="M8" t="n">
-        <v>4.270025476793968</v>
+        <v>4.27640784767643</v>
       </c>
       <c r="N8" t="n">
-        <v>30.54655736045263</v>
+        <v>30.62729628938053</v>
       </c>
       <c r="O8" t="n">
-        <v>5.526894006623669</v>
+        <v>5.534193372965976</v>
       </c>
       <c r="P8" t="n">
-        <v>388.1449263151571</v>
+        <v>388.112910449194</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31757,28 +31812,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06128229570978177</v>
+        <v>0.06194971429918631</v>
       </c>
       <c r="J9" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K9" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006248639431949421</v>
+        <v>0.006410102845690324</v>
       </c>
       <c r="M9" t="n">
-        <v>4.743848794512458</v>
+        <v>4.738755268772059</v>
       </c>
       <c r="N9" t="n">
-        <v>33.90625437750381</v>
+        <v>33.85086922749612</v>
       </c>
       <c r="O9" t="n">
-        <v>5.822907725312485</v>
+        <v>5.818149983241763</v>
       </c>
       <c r="P9" t="n">
-        <v>385.6132138223437</v>
+        <v>385.6064691070571</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31835,28 +31890,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09111551221728124</v>
+        <v>-0.09082760909053153</v>
       </c>
       <c r="J10" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K10" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01236153631109904</v>
+        <v>0.01233505970263449</v>
       </c>
       <c r="M10" t="n">
-        <v>4.951968776709221</v>
+        <v>4.944379460722588</v>
       </c>
       <c r="N10" t="n">
-        <v>37.65543601956973</v>
+        <v>37.58834341960683</v>
       </c>
       <c r="O10" t="n">
-        <v>6.136402530764237</v>
+        <v>6.130933323696061</v>
       </c>
       <c r="P10" t="n">
-        <v>384.3182320812534</v>
+        <v>384.315322625852</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31913,28 +31968,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0821643003955177</v>
+        <v>-0.08177667226932098</v>
       </c>
       <c r="J11" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K11" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01030641657274045</v>
+        <v>0.01025224442051065</v>
       </c>
       <c r="M11" t="n">
-        <v>4.673341175433577</v>
+        <v>4.666540502213178</v>
       </c>
       <c r="N11" t="n">
-        <v>36.8024624597394</v>
+        <v>36.73782844497473</v>
       </c>
       <c r="O11" t="n">
-        <v>6.066503314079652</v>
+        <v>6.061173850416661</v>
       </c>
       <c r="P11" t="n">
-        <v>379.9714597864426</v>
+        <v>379.9675425426173</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31991,28 +32046,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08593175188788159</v>
+        <v>-0.08463108450711149</v>
       </c>
       <c r="J12" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K12" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007800523111338054</v>
+        <v>0.007596220132825127</v>
       </c>
       <c r="M12" t="n">
-        <v>5.6869585128699</v>
+        <v>5.68358944950847</v>
       </c>
       <c r="N12" t="n">
-        <v>53.32122152010486</v>
+        <v>53.24756106990736</v>
       </c>
       <c r="O12" t="n">
-        <v>7.30213814715285</v>
+        <v>7.297092645013311</v>
       </c>
       <c r="P12" t="n">
-        <v>379.2332618312079</v>
+        <v>379.2201177095052</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32050,7 +32105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M552"/>
+  <dimension ref="A1:M553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69029,6 +69084,73 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-42.05964749455589,171.36372794425594</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-42.05898528117588,171.36383455777545</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-42.05832356108352,171.36394729656158</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-42.057656831476336,171.36399877864767</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-42.056992233297315,171.36407644519198</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-42.056329442812306,171.3641763318315</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-42.055668263797294,171.364296035754</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-42.05501384565017,171.3644986115857</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>-42.05435620318202,171.36466179094947</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>-42.05369605254478,171.36479434253982</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-42.053030510256306,171.36486095743635</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M553"/>
+  <dimension ref="A1:M556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25331,6 +25331,141 @@
       <c r="M553" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>404.32</v>
+      </c>
+      <c r="C554" t="n">
+        <v>403.39</v>
+      </c>
+      <c r="D554" t="n">
+        <v>402.04</v>
+      </c>
+      <c r="E554" t="n">
+        <v>404</v>
+      </c>
+      <c r="F554" t="n">
+        <v>404.25</v>
+      </c>
+      <c r="G554" t="n">
+        <v>402.25</v>
+      </c>
+      <c r="H554" t="n">
+        <v>398.77</v>
+      </c>
+      <c r="I554" t="n">
+        <v>391.48</v>
+      </c>
+      <c r="J554" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="K554" t="n">
+        <v>378.74</v>
+      </c>
+      <c r="L554" t="n">
+        <v>381.85</v>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>402.87</v>
+      </c>
+      <c r="C555" t="n">
+        <v>401.63</v>
+      </c>
+      <c r="D555" t="n">
+        <v>401.16</v>
+      </c>
+      <c r="E555" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="F555" t="n">
+        <v>401.8</v>
+      </c>
+      <c r="G555" t="n">
+        <v>399.75</v>
+      </c>
+      <c r="H555" t="n">
+        <v>397.64</v>
+      </c>
+      <c r="I555" t="n">
+        <v>391.68</v>
+      </c>
+      <c r="J555" t="n">
+        <v>382.84</v>
+      </c>
+      <c r="K555" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="L555" t="n">
+        <v>380.41</v>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>401.03</v>
+      </c>
+      <c r="C556" t="n">
+        <v>400.33</v>
+      </c>
+      <c r="D556" t="n">
+        <v>399.08</v>
+      </c>
+      <c r="E556" t="n">
+        <v>400.27</v>
+      </c>
+      <c r="F556" t="n">
+        <v>399.4</v>
+      </c>
+      <c r="G556" t="n">
+        <v>397.04</v>
+      </c>
+      <c r="H556" t="n">
+        <v>396.26</v>
+      </c>
+      <c r="I556" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="J556" t="n">
+        <v>382.26</v>
+      </c>
+      <c r="K556" t="n">
+        <v>374.7</v>
+      </c>
+      <c r="L556" t="n">
+        <v>378</v>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25345,7 +25480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B575"/>
+  <dimension ref="A1:B578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31098,6 +31233,36 @@
       </c>
       <c r="B575" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -31266,28 +31431,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1050098403195117</v>
+        <v>-0.1002319224792348</v>
       </c>
       <c r="J2" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K2" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01052485653347668</v>
+        <v>0.00969942776286592</v>
       </c>
       <c r="M2" t="n">
-        <v>6.348866372167878</v>
+        <v>6.335790760668597</v>
       </c>
       <c r="N2" t="n">
-        <v>58.99262756846855</v>
+        <v>58.78715392957336</v>
       </c>
       <c r="O2" t="n">
-        <v>7.680665828459701</v>
+        <v>7.667278130443251</v>
       </c>
       <c r="P2" t="n">
-        <v>401.1162367884553</v>
+        <v>401.0677904846698</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31344,28 +31509,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07970379785906162</v>
+        <v>-0.07669838688291659</v>
       </c>
       <c r="J3" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K3" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007197481120157057</v>
+        <v>0.006745484496808341</v>
       </c>
       <c r="M3" t="n">
-        <v>5.51082631666524</v>
+        <v>5.495350237898981</v>
       </c>
       <c r="N3" t="n">
-        <v>49.86426337181788</v>
+        <v>49.64428463786676</v>
       </c>
       <c r="O3" t="n">
-        <v>7.061463259963751</v>
+        <v>7.045870041227468</v>
       </c>
       <c r="P3" t="n">
-        <v>401.1247199319667</v>
+        <v>401.09425244997</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31422,28 +31587,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04190787895859643</v>
+        <v>-0.03767337827445187</v>
       </c>
       <c r="J4" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K4" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003020343545969362</v>
+        <v>0.002466262000324404</v>
       </c>
       <c r="M4" t="n">
-        <v>4.680729395749706</v>
+        <v>4.677826646961725</v>
       </c>
       <c r="N4" t="n">
-        <v>32.99670973321244</v>
+        <v>32.9078449165759</v>
       </c>
       <c r="O4" t="n">
-        <v>5.744276258434342</v>
+        <v>5.736535968385093</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9618185798057</v>
+        <v>397.918855178996</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31500,28 +31665,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02441238315547667</v>
+        <v>-0.01653358675676748</v>
       </c>
       <c r="J5" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K5" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001055066912332703</v>
+        <v>0.000485854004491526</v>
       </c>
       <c r="M5" t="n">
-        <v>4.601054943458334</v>
+        <v>4.616894641175957</v>
       </c>
       <c r="N5" t="n">
-        <v>32.11672273296537</v>
+        <v>32.23734323988068</v>
       </c>
       <c r="O5" t="n">
-        <v>5.667161788140989</v>
+        <v>5.67779387085166</v>
       </c>
       <c r="P5" t="n">
-        <v>395.4925124161834</v>
+        <v>395.4125682821086</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31578,28 +31743,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1143064174385608</v>
+        <v>-0.1040094833180878</v>
       </c>
       <c r="J6" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K6" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02846513987145771</v>
+        <v>0.0235188875564748</v>
       </c>
       <c r="M6" t="n">
-        <v>4.194902911757469</v>
+        <v>4.22517953612862</v>
       </c>
       <c r="N6" t="n">
-        <v>25.37671095320923</v>
+        <v>25.74200361434406</v>
       </c>
       <c r="O6" t="n">
-        <v>5.037530243403928</v>
+        <v>5.073657814076947</v>
       </c>
       <c r="P6" t="n">
-        <v>395.3365586415955</v>
+        <v>395.232141519429</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31656,28 +31821,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03814587716299542</v>
+        <v>-0.03020083538805112</v>
       </c>
       <c r="J7" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K7" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00314844638124101</v>
+        <v>0.001977211422256819</v>
       </c>
       <c r="M7" t="n">
-        <v>3.963147660108437</v>
+        <v>3.983771295785349</v>
       </c>
       <c r="N7" t="n">
-        <v>26.21672510671257</v>
+        <v>26.38606676712904</v>
       </c>
       <c r="O7" t="n">
-        <v>5.12022705616778</v>
+        <v>5.136736976634977</v>
       </c>
       <c r="P7" t="n">
-        <v>393.3462195148597</v>
+        <v>393.2656591640608</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31734,28 +31899,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07466682527530835</v>
+        <v>0.08273523404079579</v>
       </c>
       <c r="J8" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K8" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01025227541190554</v>
+        <v>0.01259215706160022</v>
       </c>
       <c r="M8" t="n">
-        <v>4.27640784767643</v>
+        <v>4.289359571143645</v>
       </c>
       <c r="N8" t="n">
-        <v>30.62729628938053</v>
+        <v>30.76286909457394</v>
       </c>
       <c r="O8" t="n">
-        <v>5.534193372965976</v>
+        <v>5.546428499004917</v>
       </c>
       <c r="P8" t="n">
-        <v>388.112910449194</v>
+        <v>388.0310848589289</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31812,28 +31977,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06194971429918631</v>
+        <v>0.0663305219853816</v>
       </c>
       <c r="J9" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K9" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006410102845690324</v>
+        <v>0.007414732274924285</v>
       </c>
       <c r="M9" t="n">
-        <v>4.738755268772059</v>
+        <v>4.736015700508106</v>
       </c>
       <c r="N9" t="n">
-        <v>33.85086922749612</v>
+        <v>33.75581342802241</v>
       </c>
       <c r="O9" t="n">
-        <v>5.818149983241763</v>
+        <v>5.809975337987452</v>
       </c>
       <c r="P9" t="n">
-        <v>385.6064691070571</v>
+        <v>385.5620364160606</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31890,28 +32055,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09082760909053153</v>
+        <v>-0.08963571805926564</v>
       </c>
       <c r="J10" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K10" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01233505970263449</v>
+        <v>0.01216447185922465</v>
       </c>
       <c r="M10" t="n">
-        <v>4.944379460722588</v>
+        <v>4.923308893385908</v>
       </c>
       <c r="N10" t="n">
-        <v>37.58834341960683</v>
+        <v>37.39409137650805</v>
       </c>
       <c r="O10" t="n">
-        <v>6.130933323696061</v>
+        <v>6.11507083986016</v>
       </c>
       <c r="P10" t="n">
-        <v>384.315322625852</v>
+        <v>384.3032423947982</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31968,28 +32133,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08177667226932098</v>
+        <v>-0.08287616648278194</v>
       </c>
       <c r="J11" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K11" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01025224442051065</v>
+        <v>0.01065266117615993</v>
       </c>
       <c r="M11" t="n">
-        <v>4.666540502213178</v>
+        <v>4.650902805586814</v>
       </c>
       <c r="N11" t="n">
-        <v>36.73782844497473</v>
+        <v>36.55942711986145</v>
       </c>
       <c r="O11" t="n">
-        <v>6.061173850416661</v>
+        <v>6.046439209969901</v>
       </c>
       <c r="P11" t="n">
-        <v>379.9675425426173</v>
+        <v>379.9787150357579</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32046,28 +32211,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08463108450711149</v>
+        <v>-0.08125740927301059</v>
       </c>
       <c r="J12" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="K12" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007596220132825127</v>
+        <v>0.007086078575131216</v>
       </c>
       <c r="M12" t="n">
-        <v>5.68358944950847</v>
+        <v>5.670872930339913</v>
       </c>
       <c r="N12" t="n">
-        <v>53.24756106990736</v>
+        <v>53.02503657555461</v>
       </c>
       <c r="O12" t="n">
-        <v>7.297092645013311</v>
+        <v>7.281829205327093</v>
       </c>
       <c r="P12" t="n">
-        <v>379.2201177095052</v>
+        <v>379.1859166684443</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32105,7 +32270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M553"/>
+  <dimension ref="A1:M556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69151,6 +69316,207 @@
         </is>
       </c>
     </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-42.05964599375146,171.36370956684218</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-42.05898305451364,171.36380729221892</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-42.05832052029831,171.36391006204184</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-42.05765473236386,171.36397307508474</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-42.05699061483462,171.36405662722876</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-42.056328697346,171.36416720365102</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-42.055668224562694,171.36429555532837</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-42.05501148180996,171.3644696662298</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>-42.054355016377706,171.36464725836512</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>-42.053696170242766,171.36479578377325</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>-42.053029205776696,171.36484498393182</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-42.05964741608254,171.36372698334543</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-42.058984780913136,171.3638284320335</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-42.05832138349018,171.36392063184059</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-42.057656596062145,171.363995896005</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-42.05699301800527,171.36408605390181</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-42.056331149535076,171.3641972305613</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-42.055669332939345,171.36430912735332</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-42.05501128564031,171.36446726412572</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>-42.05435605605762,171.36465998938937</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>-42.053697974943006,171.36481788268634</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-42.05303061814549,171.3648622785533</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-42.059649220967835,171.36374908428868</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-42.058986056092074,171.36384404667007</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-42.058323423758,171.36394561500254</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-42.05765839109359,171.36401787615588</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-42.05699537212435,171.36411488003293</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-42.05633380769918,171.36422977973493</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-42.055670686529936,171.3643257020394</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-42.0550121978287,171.36447843390997</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-42.05435662493848,171.3646669554217</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-42.053700132731194,171.3648443053016</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-42.053032981895804,171.36489122302586</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M556"/>
+  <dimension ref="A1:M559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25464,6 +25464,141 @@
         <v>378</v>
       </c>
       <c r="M556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:05+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>400.34</v>
+      </c>
+      <c r="C557" t="n">
+        <v>400.14</v>
+      </c>
+      <c r="D557" t="n">
+        <v>398.96</v>
+      </c>
+      <c r="E557" t="n">
+        <v>399.78</v>
+      </c>
+      <c r="F557" t="n">
+        <v>398.16</v>
+      </c>
+      <c r="G557" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="H557" t="n">
+        <v>395.8</v>
+      </c>
+      <c r="I557" t="n">
+        <v>391.36</v>
+      </c>
+      <c r="J557" t="n">
+        <v>382.73</v>
+      </c>
+      <c r="K557" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="L557" t="n">
+        <v>376.95</v>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>399.84</v>
+      </c>
+      <c r="C558" t="n">
+        <v>399.96</v>
+      </c>
+      <c r="D558" t="n">
+        <v>398</v>
+      </c>
+      <c r="E558" t="n">
+        <v>398.47</v>
+      </c>
+      <c r="F558" t="n">
+        <v>397.42</v>
+      </c>
+      <c r="G558" t="n">
+        <v>394.65</v>
+      </c>
+      <c r="H558" t="n">
+        <v>395.77</v>
+      </c>
+      <c r="I558" t="n">
+        <v>390.64</v>
+      </c>
+      <c r="J558" t="n">
+        <v>382.27</v>
+      </c>
+      <c r="K558" t="n">
+        <v>373.67</v>
+      </c>
+      <c r="L558" t="n">
+        <v>375.33</v>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>398.52</v>
+      </c>
+      <c r="C559" t="n">
+        <v>399.11</v>
+      </c>
+      <c r="D559" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="E559" t="n">
+        <v>395.64</v>
+      </c>
+      <c r="F559" t="n">
+        <v>394.43</v>
+      </c>
+      <c r="G559" t="n">
+        <v>389.46</v>
+      </c>
+      <c r="H559" t="n">
+        <v>393.31</v>
+      </c>
+      <c r="I559" t="n">
+        <v>391.84</v>
+      </c>
+      <c r="J559" t="n">
+        <v>385.12</v>
+      </c>
+      <c r="K559" t="n">
+        <v>374.04</v>
+      </c>
+      <c r="L559" t="n">
+        <v>372.53</v>
+      </c>
+      <c r="M559" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25480,7 +25615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31263,6 +31398,36 @@
       </c>
       <c r="B578" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>
@@ -31431,28 +31596,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1002319224792348</v>
+        <v>-0.09897944050978111</v>
       </c>
       <c r="J2" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00969942776286592</v>
+        <v>0.009576441061790897</v>
       </c>
       <c r="M2" t="n">
-        <v>6.335790760668597</v>
+        <v>6.307225353059571</v>
       </c>
       <c r="N2" t="n">
-        <v>58.78715392957336</v>
+        <v>58.48148983188935</v>
       </c>
       <c r="O2" t="n">
-        <v>7.667278130443251</v>
+        <v>7.647319127111759</v>
       </c>
       <c r="P2" t="n">
-        <v>401.0677904846698</v>
+        <v>401.0550504708215</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31509,28 +31674,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07669838688291659</v>
+        <v>-0.07596355769899812</v>
       </c>
       <c r="J3" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K3" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006745484496808341</v>
+        <v>0.006699515483797103</v>
       </c>
       <c r="M3" t="n">
-        <v>5.495350237898981</v>
+        <v>5.469262795201693</v>
       </c>
       <c r="N3" t="n">
-        <v>49.64428463786676</v>
+        <v>49.38095236602884</v>
       </c>
       <c r="O3" t="n">
-        <v>7.045870041227468</v>
+        <v>7.02715819987204</v>
       </c>
       <c r="P3" t="n">
-        <v>401.09425244997</v>
+        <v>401.0867779665999</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31587,28 +31752,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03767337827445187</v>
+        <v>-0.03636635040640777</v>
       </c>
       <c r="J4" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002466262000324404</v>
+        <v>0.002326473425455222</v>
       </c>
       <c r="M4" t="n">
-        <v>4.677826646961725</v>
+        <v>4.659559386516805</v>
       </c>
       <c r="N4" t="n">
-        <v>32.9078449165759</v>
+        <v>32.74057371198445</v>
       </c>
       <c r="O4" t="n">
-        <v>5.736535968385093</v>
+        <v>5.721937933251676</v>
       </c>
       <c r="P4" t="n">
-        <v>397.918855178996</v>
+        <v>397.9055493995783</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31665,28 +31830,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01653358675676748</v>
+        <v>-0.01333335842690745</v>
       </c>
       <c r="J5" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K5" t="n">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000485854004491526</v>
+        <v>0.0003193481956645927</v>
       </c>
       <c r="M5" t="n">
-        <v>4.616894641175957</v>
+        <v>4.608385327870696</v>
       </c>
       <c r="N5" t="n">
-        <v>32.23734323988068</v>
+        <v>32.12716641444321</v>
       </c>
       <c r="O5" t="n">
-        <v>5.67779387085166</v>
+        <v>5.668083134044807</v>
       </c>
       <c r="P5" t="n">
-        <v>395.4125682821086</v>
+        <v>395.3799938123973</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31743,28 +31908,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1040094833180878</v>
+        <v>-0.09950100035900629</v>
       </c>
       <c r="J6" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K6" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0235188875564748</v>
+        <v>0.0217417029886291</v>
       </c>
       <c r="M6" t="n">
-        <v>4.22517953612862</v>
+        <v>4.22536715816874</v>
       </c>
       <c r="N6" t="n">
-        <v>25.74200361434406</v>
+        <v>25.7114454237572</v>
       </c>
       <c r="O6" t="n">
-        <v>5.073657814076947</v>
+        <v>5.070645464214315</v>
       </c>
       <c r="P6" t="n">
-        <v>395.232141519429</v>
+        <v>395.1862711815643</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31821,28 +31986,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03020083538805112</v>
+        <v>-0.02925598596814272</v>
       </c>
       <c r="J7" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K7" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001977211422256819</v>
+        <v>0.001875544704379339</v>
       </c>
       <c r="M7" t="n">
-        <v>3.983771295785349</v>
+        <v>3.978270515455991</v>
       </c>
       <c r="N7" t="n">
-        <v>26.38606676712904</v>
+        <v>26.29047125738917</v>
       </c>
       <c r="O7" t="n">
-        <v>5.136736976634977</v>
+        <v>5.127423452123803</v>
       </c>
       <c r="P7" t="n">
-        <v>393.2656591640608</v>
+        <v>393.256070366716</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31899,28 +32064,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08273523404079579</v>
+        <v>0.0877827386124915</v>
       </c>
       <c r="J8" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K8" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01259215706160022</v>
+        <v>0.01427030424420439</v>
       </c>
       <c r="M8" t="n">
-        <v>4.289359571143645</v>
+        <v>4.288899804462166</v>
       </c>
       <c r="N8" t="n">
-        <v>30.76286909457394</v>
+        <v>30.72235305482607</v>
       </c>
       <c r="O8" t="n">
-        <v>5.546428499004917</v>
+        <v>5.542774851536554</v>
       </c>
       <c r="P8" t="n">
-        <v>388.0310848589289</v>
+        <v>387.9797241606789</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31977,28 +32142,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0663305219853816</v>
+        <v>0.07055974579508845</v>
       </c>
       <c r="J9" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K9" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007414732274924285</v>
+        <v>0.008465341131027038</v>
       </c>
       <c r="M9" t="n">
-        <v>4.736015700508106</v>
+        <v>4.73244800079107</v>
       </c>
       <c r="N9" t="n">
-        <v>33.75581342802241</v>
+        <v>33.65805899530061</v>
       </c>
       <c r="O9" t="n">
-        <v>5.809975337987452</v>
+        <v>5.801556601059806</v>
       </c>
       <c r="P9" t="n">
-        <v>385.5620364160606</v>
+        <v>385.5189885865353</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32055,28 +32220,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08963571805926564</v>
+        <v>-0.0880686464727706</v>
       </c>
       <c r="J10" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K10" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01216447185922465</v>
+        <v>0.01188692493517718</v>
       </c>
       <c r="M10" t="n">
-        <v>4.923308893385908</v>
+        <v>4.90422050741524</v>
       </c>
       <c r="N10" t="n">
-        <v>37.39409137650805</v>
+        <v>37.21271749033197</v>
       </c>
       <c r="O10" t="n">
-        <v>6.11507083986016</v>
+        <v>6.100222741042492</v>
       </c>
       <c r="P10" t="n">
-        <v>384.3032423947982</v>
+        <v>384.2872809013605</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32133,28 +32298,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08287616648278194</v>
+        <v>-0.08669392323777093</v>
       </c>
       <c r="J11" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K11" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01065266117615993</v>
+        <v>0.01176715933729822</v>
       </c>
       <c r="M11" t="n">
-        <v>4.650902805586814</v>
+        <v>4.64733245627411</v>
       </c>
       <c r="N11" t="n">
-        <v>36.55942711986145</v>
+        <v>36.43146019119648</v>
       </c>
       <c r="O11" t="n">
-        <v>6.046439209969901</v>
+        <v>6.035847926447159</v>
       </c>
       <c r="P11" t="n">
-        <v>379.9787150357579</v>
+        <v>380.0175726705968</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32211,28 +32376,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08125740927301059</v>
+        <v>-0.08348553469377079</v>
       </c>
       <c r="J12" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K12" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007086078575131216</v>
+        <v>0.007564168413554673</v>
       </c>
       <c r="M12" t="n">
-        <v>5.670872930339913</v>
+        <v>5.650586617008808</v>
       </c>
       <c r="N12" t="n">
-        <v>53.02503657555461</v>
+        <v>52.7807222550671</v>
       </c>
       <c r="O12" t="n">
-        <v>7.281829205327093</v>
+        <v>7.265034222566822</v>
       </c>
       <c r="P12" t="n">
-        <v>379.1859166684443</v>
+        <v>379.2086113280855</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32270,7 +32435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M556"/>
+  <dimension ref="A1:M559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69517,6 +69682,207 @@
         </is>
       </c>
     </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:05+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-42.05964989779872,171.36375737214277</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-42.0589862424642,171.3638463288093</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-42.05832354146559,171.36394705633884</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-42.057658871729714,171.36402376155172</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-42.056996588416375,171.3641297735349</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-42.056334886656174,171.36424299157744</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-42.05567113772627,171.36433122693492</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-42.05501159951171,171.36447110749228</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-42.054356163948846,171.36466131053345</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-42.053699946376994,171.3648420233484</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-42.05303401174325,171.36490383368894</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-42.05965038825551,171.36376337783423</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-42.058986419027235,171.36384849083598</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-42.05832448312567,171.3639585870296</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-42.05766015669418,171.36403949597778</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-42.05699731426716,171.36413866159285</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-42.05633615197652,171.36425848546617</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-42.0556711671521,171.36433158725418</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-42.055012305721895,171.3644797550673</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-42.05435661513021,171.3646668353177</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-42.05370114296631,171.36485667589034</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-42.05303560064803,171.36492329014143</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-42.059651683059954,171.36377923286025</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-42.05898725279655,171.36385870040655</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-42.058325022617936,171.3639651931547</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-42.057662932602504,171.36407348714488</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-42.057000247089675,171.3641745741536</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-42.05634124266293,171.36432082135084</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-42.05567358006702,171.3643611334361</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-42.055011128704564,171.36446534244243</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-42.05435381976323,171.36463260567737</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>-42.05370078006647,171.36485223208658</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>-42.05303834689548,171.36495691858033</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M559"/>
+  <dimension ref="A1:M561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25601,6 +25601,96 @@
       <c r="M559" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>396.97</v>
+      </c>
+      <c r="C560" t="n">
+        <v>398.59</v>
+      </c>
+      <c r="D560" t="n">
+        <v>397.43</v>
+      </c>
+      <c r="E560" t="n">
+        <v>395.17</v>
+      </c>
+      <c r="F560" t="n">
+        <v>393.76</v>
+      </c>
+      <c r="G560" t="n">
+        <v>387.13</v>
+      </c>
+      <c r="H560" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="I560" t="n">
+        <v>391.14</v>
+      </c>
+      <c r="J560" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="K560" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="L560" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:18:47+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>396.31</v>
+      </c>
+      <c r="C561" t="n">
+        <v>399.29</v>
+      </c>
+      <c r="D561" t="n">
+        <v>397.41</v>
+      </c>
+      <c r="E561" t="n">
+        <v>395.6</v>
+      </c>
+      <c r="F561" t="n">
+        <v>393.24</v>
+      </c>
+      <c r="G561" t="n">
+        <v>386.36</v>
+      </c>
+      <c r="H561" t="n">
+        <v>390.97</v>
+      </c>
+      <c r="I561" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="J561" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="K561" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="L561" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25615,7 +25705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B581"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31428,6 +31518,26 @@
       </c>
       <c r="B581" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -31596,28 +31706,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09897944050978111</v>
+        <v>-0.1002347860627169</v>
       </c>
       <c r="J2" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K2" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009576441061790897</v>
+        <v>0.009897467817380101</v>
       </c>
       <c r="M2" t="n">
-        <v>6.307225353059571</v>
+        <v>6.291725085739076</v>
       </c>
       <c r="N2" t="n">
-        <v>58.48148983188935</v>
+        <v>58.28398544025447</v>
       </c>
       <c r="O2" t="n">
-        <v>7.647319127111759</v>
+        <v>7.634394896797943</v>
       </c>
       <c r="P2" t="n">
-        <v>401.0550504708215</v>
+        <v>401.0678853685436</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31674,28 +31784,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07596355769899812</v>
+        <v>-0.07604183546879263</v>
       </c>
       <c r="J3" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K3" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006699515483797103</v>
+        <v>0.006768647925709415</v>
       </c>
       <c r="M3" t="n">
-        <v>5.469262795201693</v>
+        <v>5.451011013315525</v>
       </c>
       <c r="N3" t="n">
-        <v>49.38095236602884</v>
+        <v>49.20507635992553</v>
       </c>
       <c r="O3" t="n">
-        <v>7.02715819987204</v>
+        <v>7.014633016767558</v>
       </c>
       <c r="P3" t="n">
-        <v>401.0867779665999</v>
+        <v>401.0875771922014</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31752,28 +31862,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03636635040640777</v>
+        <v>-0.03601650682800146</v>
       </c>
       <c r="J4" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K4" t="n">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002326473425455222</v>
+        <v>0.002300900246314685</v>
       </c>
       <c r="M4" t="n">
-        <v>4.659559386516805</v>
+        <v>4.644717529968549</v>
       </c>
       <c r="N4" t="n">
-        <v>32.74057371198445</v>
+        <v>32.62428813537903</v>
       </c>
       <c r="O4" t="n">
-        <v>5.721937933251676</v>
+        <v>5.711767514121966</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9055493995783</v>
+        <v>397.9019706065587</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31830,28 +31940,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01333335842690745</v>
+        <v>-0.01307367848642554</v>
       </c>
       <c r="J5" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K5" t="n">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003193481956645927</v>
+        <v>0.0003095798802651428</v>
       </c>
       <c r="M5" t="n">
-        <v>4.608385327870696</v>
+        <v>4.593205305754969</v>
       </c>
       <c r="N5" t="n">
-        <v>32.12716641444321</v>
+        <v>32.01286029094521</v>
       </c>
       <c r="O5" t="n">
-        <v>5.668083134044807</v>
+        <v>5.657990835176848</v>
       </c>
       <c r="P5" t="n">
-        <v>395.3799938123973</v>
+        <v>395.3773366953874</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31908,28 +32018,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09950100035900629</v>
+        <v>-0.09880380284433275</v>
       </c>
       <c r="J6" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K6" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0217417029886291</v>
+        <v>0.02161616627182039</v>
       </c>
       <c r="M6" t="n">
-        <v>4.22536715816874</v>
+        <v>4.213771264764005</v>
       </c>
       <c r="N6" t="n">
-        <v>25.7114454237572</v>
+        <v>25.62324617616073</v>
       </c>
       <c r="O6" t="n">
-        <v>5.070645464214315</v>
+        <v>5.061940949493655</v>
       </c>
       <c r="P6" t="n">
-        <v>395.1862711815643</v>
+        <v>395.179144197605</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31986,28 +32096,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02925598596814272</v>
+        <v>-0.03333261977977148</v>
       </c>
       <c r="J7" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K7" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001875544704379339</v>
+        <v>0.002442664954475648</v>
       </c>
       <c r="M7" t="n">
-        <v>3.978270515455991</v>
+        <v>3.982780066251936</v>
       </c>
       <c r="N7" t="n">
-        <v>26.29047125738917</v>
+        <v>26.31292295982699</v>
       </c>
       <c r="O7" t="n">
-        <v>5.127423452123803</v>
+        <v>5.129612359606424</v>
       </c>
       <c r="P7" t="n">
-        <v>393.256070366716</v>
+        <v>393.2977486757796</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32064,28 +32174,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0877827386124915</v>
+        <v>0.08859093232361981</v>
       </c>
       <c r="J8" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K8" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01427030424420439</v>
+        <v>0.01464699541016545</v>
       </c>
       <c r="M8" t="n">
-        <v>4.288899804462166</v>
+        <v>4.277154696806444</v>
       </c>
       <c r="N8" t="n">
-        <v>30.72235305482607</v>
+        <v>30.61808868513572</v>
       </c>
       <c r="O8" t="n">
-        <v>5.542774851536554</v>
+        <v>5.533361427300382</v>
       </c>
       <c r="P8" t="n">
-        <v>387.9797241606789</v>
+        <v>387.9714631395157</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32142,28 +32252,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07055974579508845</v>
+        <v>0.07257979792297944</v>
       </c>
       <c r="J9" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K9" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008465341131027038</v>
+        <v>0.009018054640032358</v>
       </c>
       <c r="M9" t="n">
-        <v>4.73244800079107</v>
+        <v>4.725883182967833</v>
       </c>
       <c r="N9" t="n">
-        <v>33.65805899530061</v>
+        <v>33.56917141805803</v>
       </c>
       <c r="O9" t="n">
-        <v>5.801556601059806</v>
+        <v>5.793890870395992</v>
       </c>
       <c r="P9" t="n">
-        <v>385.5189885865353</v>
+        <v>385.4983393817018</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32220,28 +32330,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0880686464727706</v>
+        <v>-0.08629060875187676</v>
       </c>
       <c r="J10" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K10" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01188692493517718</v>
+        <v>0.01150436083243045</v>
       </c>
       <c r="M10" t="n">
-        <v>4.90422050741524</v>
+        <v>4.895103447555997</v>
       </c>
       <c r="N10" t="n">
-        <v>37.21271749033197</v>
+        <v>37.10184963953333</v>
       </c>
       <c r="O10" t="n">
-        <v>6.100222741042492</v>
+        <v>6.091128765633948</v>
       </c>
       <c r="P10" t="n">
-        <v>384.2872809013605</v>
+        <v>384.2691032587136</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32298,28 +32408,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08669392323777093</v>
+        <v>-0.08939830602952201</v>
       </c>
       <c r="J11" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K11" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01176715933729822</v>
+        <v>0.01258869563002418</v>
       </c>
       <c r="M11" t="n">
-        <v>4.64733245627411</v>
+        <v>4.645837372032635</v>
       </c>
       <c r="N11" t="n">
-        <v>36.43146019119648</v>
+        <v>36.35232340846222</v>
       </c>
       <c r="O11" t="n">
-        <v>6.035847926447159</v>
+        <v>6.029288797898325</v>
       </c>
       <c r="P11" t="n">
-        <v>380.0175726705968</v>
+        <v>380.0452207301719</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32376,28 +32486,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08348553469377079</v>
+        <v>-0.08728791563602481</v>
       </c>
       <c r="J12" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K12" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007564168413554673</v>
+        <v>0.008315438951810861</v>
       </c>
       <c r="M12" t="n">
-        <v>5.650586617008808</v>
+        <v>5.64802971855338</v>
       </c>
       <c r="N12" t="n">
-        <v>52.7807222550671</v>
+        <v>52.69299100649397</v>
       </c>
       <c r="O12" t="n">
-        <v>7.265034222566822</v>
+        <v>7.258993801243666</v>
       </c>
       <c r="P12" t="n">
-        <v>379.2086113280855</v>
+        <v>379.247484692495</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32435,7 +32545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M559"/>
+  <dimension ref="A1:M561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69883,6 +69993,140 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-42.05965320347148,171.36379785050534</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-42.05898776286674,171.36386494626163</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-42.058325042235836,171.36396543337744</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-42.05766339361812,171.36407913232136</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-42.05700090427579,171.3641826214503</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-42.0563435280661,171.36434880644333</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-42.05567489441586,171.36437722769884</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-42.05501181529822,171.36447374980688</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>-42.05435449653722,171.36464089285315</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-42.05370092718805,171.36485403362863</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>-42.053039229615784,171.3649677277221</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:18:47+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-42.0596538508716,171.363805778019</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-42.05898707623371,171.36385653837982</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-42.05832506185371,171.3639656736002</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-42.05766297183789,171.36407396758543</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-42.0570014143303,171.36418886711354</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-42.056344283326595,171.3643580547362</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-42.055675875271746,171.36438923834316</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-42.05501357101351,171.36449524863968</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>-42.05435449653722,171.36464089285315</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>-42.05370092718805,171.36485403362863</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-42.053039229615784,171.3649677277221</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
